--- a/winners_record.xlsx
+++ b/winners_record.xlsx
@@ -23,12 +23,40 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>Asheetuu Badhaadhaa</t>
+  </si>
+  <si>
+    <t>Tigisti  Mangashaa</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -51,13 +79,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -336,9 +368,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/winners_record.xlsx
+++ b/winners_record.xlsx
@@ -24,12 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Asheetuu Badhaadhaa</t>
   </si>
   <si>
     <t>Tigisti  Mangashaa</t>
+  </si>
+  <si>
+    <t>Gabbisaa Katamaa</t>
   </si>
 </sst>
 </file>
@@ -368,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -391,6 +394,14 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/winners_record.xlsx
+++ b/winners_record.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Asheetuu Badhaadhaa</t>
   </si>
@@ -34,32 +34,21 @@
   <si>
     <t>Gabbisaa Katamaa</t>
   </si>
+  <si>
+    <t>Maqaa</t>
+  </si>
+  <si>
+    <t>Amma Mallaqaa</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -82,17 +71,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -371,34 +356,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>3000</v>
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>3000</v>
       </c>
     </row>
